--- a/documentation/integrations/DataExchangeSpecification_v1.xlsx
+++ b/documentation/integrations/DataExchangeSpecification_v1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\io\Energy\Specifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\io\41-19-12-2025\documentation\integrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B63B7AD-F1DB-4C05-BAB5-4BF5A65053EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D066FE-BB79-4E52-B1AA-49F357D8BDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -283,9 +283,6 @@
     <t>Fixed Value</t>
   </si>
   <si>
-    <t>DD-MM-YYYYhh:mm:ss[+|-]hh:mm</t>
-  </si>
-  <si>
     <t>Лица от домакинството</t>
   </si>
   <si>
@@ -1195,9 +1192,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>DD-MM-YYYY</t>
-  </si>
-  <si>
     <t>certificateDate</t>
   </si>
   <si>
@@ -1292,6 +1286,12 @@
   </si>
   <si>
     <t>Бащино име</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DDhh:mm:ss[+|-]hh:mm</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
   </si>
 </sst>
 </file>
@@ -3531,157 +3531,157 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="115" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3802,7 +3802,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -3856,7 +3856,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="61" t="s">
         <v>59</v>
@@ -3916,7 +3916,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -3933,7 +3933,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="156" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -4003,18 +4003,18 @@
       <c r="G13" s="24"/>
       <c r="H13" s="151"/>
       <c r="I13" s="153" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>54</v>
       </c>
       <c r="K13" s="64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="156" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -4028,45 +4028,45 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" s="24"/>
       <c r="I14" s="41"/>
       <c r="J14" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K14" s="68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="85" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B15" s="144" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="144" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="143"/>
       <c r="E15" s="143"/>
       <c r="F15" s="143"/>
       <c r="G15" s="143"/>
       <c r="H15" s="54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I15" s="143"/>
       <c r="J15" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="K15" s="79" t="s">
         <v>238</v>
-      </c>
-      <c r="K15" s="79" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>21</v>
@@ -4082,18 +4082,18 @@
       <c r="G16" s="24"/>
       <c r="H16" s="151"/>
       <c r="I16" s="153" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K16" s="64" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -4102,7 +4102,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -4110,15 +4110,15 @@
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" s="68" t="s">
         <v>253</v>
-      </c>
-      <c r="K17" s="68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="155" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
@@ -4133,32 +4133,32 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="85" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B19" s="54" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="154"/>
       <c r="E19" s="54"/>
       <c r="F19" s="54"/>
       <c r="G19" s="142"/>
       <c r="H19" s="54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I19" s="54"/>
       <c r="J19" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="K19" s="79" t="s">
         <v>240</v>
-      </c>
-      <c r="K19" s="79" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B20" s="41" t="s">
         <v>21</v>
@@ -4174,18 +4174,18 @@
       <c r="G20" s="24"/>
       <c r="H20" s="151"/>
       <c r="I20" s="153" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J20" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="K20" s="64" t="s">
         <v>259</v>
-      </c>
-      <c r="K20" s="64" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>21</v>
@@ -4194,7 +4194,7 @@
         <v>22</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -4202,15 +4202,15 @@
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K21" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="155" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" s="53"/>
       <c r="C22" s="53"/>
@@ -4355,7 +4355,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -4408,7 +4408,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -4468,7 +4468,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -4485,7 +4485,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="143" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" s="144" t="s">
         <v>21</v>
@@ -4554,7 +4554,7 @@
       <c r="H13" s="143"/>
       <c r="I13" s="143"/>
       <c r="J13" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K13" s="142" t="s">
         <v>2</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -4574,22 +4574,22 @@
         <v>29</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="41"/>
       <c r="J14" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K14" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="148" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>51</v>
@@ -4601,24 +4601,24 @@
         <v>29</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I15" s="41"/>
       <c r="J15" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K15" s="61" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>53</v>
@@ -4630,22 +4630,22 @@
         <v>29</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="K16" s="61" t="s">
         <v>165</v>
-      </c>
-      <c r="K16" s="61" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="148" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>53</v>
@@ -4657,22 +4657,22 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K17" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -4684,22 +4684,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" s="61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>53</v>
@@ -4711,22 +4711,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="I19" s="41"/>
       <c r="J19" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>53</v>
@@ -4738,22 +4738,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="I20" s="41"/>
       <c r="J20" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K20" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" s="72"/>
       <c r="C21" s="72"/>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B22" s="43" t="s">
         <v>21</v>
@@ -4783,10 +4783,10 @@
       <c r="H22" s="45"/>
       <c r="I22" s="45"/>
       <c r="J22" s="46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K22" s="75" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
@@ -4807,18 +4807,18 @@
       <c r="G23" s="26"/>
       <c r="H23" s="48"/>
       <c r="I23" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J23" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>21</v>
@@ -4831,20 +4831,20 @@
       </c>
       <c r="F24" s="34"/>
       <c r="G24" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H24" s="34"/>
       <c r="I24" s="47"/>
       <c r="J24" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K24" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>21</v>
@@ -4856,22 +4856,22 @@
         <v>29</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="41"/>
       <c r="J25" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K25" s="83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="63" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>53</v>
@@ -4883,22 +4883,22 @@
         <v>29</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
       <c r="I26" s="41"/>
       <c r="J26" s="24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K26" s="83" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>21</v>
@@ -4910,22 +4910,22 @@
         <v>29</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
       <c r="I27" s="41"/>
       <c r="J27" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
@@ -4940,7 +4940,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>21</v>
@@ -4955,15 +4955,15 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K29" s="86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>53</v>
@@ -4975,22 +4975,22 @@
         <v>29</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
       <c r="I30" s="41"/>
       <c r="J30" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K30" s="83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>53</v>
@@ -5002,22 +5002,22 @@
         <v>29</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
       <c r="I31" s="41"/>
       <c r="J31" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K31" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" s="24" t="s">
         <v>53</v>
@@ -5029,22 +5029,22 @@
         <v>29</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
       <c r="I32" s="41"/>
       <c r="J32" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K32" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B33" s="72"/>
       <c r="C33" s="72"/>
@@ -5189,7 +5189,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -5242,7 +5242,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -5302,7 +5302,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -5319,7 +5319,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="13" spans="1:11" s="95" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="168" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>21</v>
@@ -5392,15 +5392,15 @@
       <c r="H13" s="30"/>
       <c r="I13" s="164"/>
       <c r="J13" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" s="169" t="s">
         <v>301</v>
-      </c>
-      <c r="K13" s="169" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B14" s="41" t="s">
         <v>21</v>
@@ -5414,22 +5414,22 @@
       <c r="E14" s="24"/>
       <c r="F14" s="41"/>
       <c r="G14" s="56" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K14" s="76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="165" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>53</v>
@@ -5441,22 +5441,22 @@
         <v>29</v>
       </c>
       <c r="E15" s="167" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K15" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B16" s="144" t="s">
         <v>51</v>
@@ -5469,11 +5469,11 @@
       <c r="F16" s="143"/>
       <c r="G16" s="143"/>
       <c r="H16" s="54" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I16" s="143"/>
       <c r="J16" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K16" s="79" t="s">
         <v>2</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -5493,22 +5493,22 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K17" s="68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>51</v>
@@ -5520,24 +5520,24 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K18" s="68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>53</v>
@@ -5549,22 +5549,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="I19" s="41"/>
       <c r="J19" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="K19" s="68" t="s">
         <v>165</v>
-      </c>
-      <c r="K19" s="68" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>53</v>
@@ -5576,22 +5576,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="I20" s="41"/>
       <c r="J20" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K20" s="68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="69" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>53</v>
@@ -5603,22 +5603,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K21" s="68" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>53</v>
@@ -5630,22 +5630,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K22" s="68" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -5657,22 +5657,22 @@
         <v>29</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K23" s="68" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
@@ -5687,7 +5687,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>51</v>
@@ -5700,14 +5700,14 @@
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I25" s="45"/>
       <c r="J25" s="46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K25" s="75" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
@@ -5728,18 +5728,18 @@
       <c r="G26" s="26"/>
       <c r="H26" s="48"/>
       <c r="I26" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J26" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>21</v>
@@ -5752,20 +5752,20 @@
       </c>
       <c r="F27" s="34"/>
       <c r="G27" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" s="34"/>
       <c r="I27" s="47"/>
       <c r="J27" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>21</v>
@@ -5777,22 +5777,22 @@
         <v>29</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="41"/>
       <c r="J28" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K28" s="83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="63" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>53</v>
@@ -5804,22 +5804,22 @@
         <v>29</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="41"/>
       <c r="J29" s="24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K29" s="83" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>21</v>
@@ -5831,22 +5831,22 @@
         <v>29</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
       <c r="I30" s="41"/>
       <c r="J30" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K30" s="83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B31" s="72"/>
       <c r="C31" s="72"/>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>51</v>
@@ -5874,19 +5874,19 @@
       <c r="F32" s="11"/>
       <c r="G32" s="106"/>
       <c r="H32" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I32" s="11"/>
       <c r="J32" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K32" s="86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>51</v>
@@ -5898,24 +5898,24 @@
         <v>29</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I33" s="41"/>
       <c r="J33" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K33" s="83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>51</v>
@@ -5927,24 +5927,24 @@
         <v>29</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I34" s="41"/>
       <c r="J34" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K34" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>51</v>
@@ -5956,24 +5956,24 @@
         <v>29</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I35" s="41"/>
       <c r="J35" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K35" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B36" s="72"/>
       <c r="C36" s="72"/>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>53</v>
@@ -5998,24 +5998,24 @@
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="106"/>
       <c r="H37" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K37" s="86" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B38" s="24" t="s">
         <v>53</v>
@@ -6024,25 +6024,25 @@
         <v>50</v>
       </c>
       <c r="D38" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>331</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>332</v>
       </c>
       <c r="F38" s="24"/>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
       <c r="I38" s="41"/>
       <c r="J38" s="24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K38" s="77" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="157" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" s="24" t="s">
         <v>53</v>
@@ -6051,25 +6051,25 @@
         <v>50</v>
       </c>
       <c r="D39" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>331</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>332</v>
       </c>
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
       <c r="I39" s="41"/>
       <c r="J39" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K39" s="77" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" s="72"/>
       <c r="C40" s="72"/>
@@ -6215,7 +6215,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -6268,7 +6268,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -6328,7 +6328,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -6345,7 +6345,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -6399,7 +6399,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>21</v>
@@ -6411,22 +6411,22 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
       <c r="I13" s="41"/>
       <c r="J13" s="55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -6435,25 +6435,25 @@
         <v>22</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="41"/>
       <c r="J14" s="55" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K14" s="61" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>21</v>
@@ -6462,25 +6462,25 @@
         <v>22</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="41"/>
       <c r="J15" s="55" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K15" s="61" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>21</v>
@@ -6496,18 +6496,18 @@
       <c r="G16" s="24"/>
       <c r="H16" s="151"/>
       <c r="I16" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="J16" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="J16" s="55" t="s">
-        <v>387</v>
-      </c>
       <c r="K16" s="61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -6523,18 +6523,18 @@
       <c r="G17" s="24"/>
       <c r="H17" s="151"/>
       <c r="I17" s="24" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J17" s="55" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K17" s="61" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -6546,22 +6546,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K18" s="61" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B19" s="43" t="s">
         <v>21</v>
@@ -6576,10 +6576,10 @@
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
       <c r="J19" s="46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K19" s="75" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
@@ -6600,18 +6600,18 @@
       <c r="G20" s="26"/>
       <c r="H20" s="48"/>
       <c r="I20" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>21</v>
@@ -6624,20 +6624,20 @@
       </c>
       <c r="F21" s="34"/>
       <c r="G21" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21" s="34"/>
       <c r="I21" s="47"/>
       <c r="J21" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>21</v>
@@ -6649,22 +6649,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K22" s="83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="63" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -6676,22 +6676,22 @@
         <v>29</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K23" s="83" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>21</v>
@@ -6703,22 +6703,22 @@
         <v>29</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="41"/>
       <c r="J24" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K24" s="83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>21</v>
@@ -6748,15 +6748,15 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K26" s="86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>53</v>
@@ -6768,22 +6768,22 @@
         <v>29</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
       <c r="I27" s="41"/>
       <c r="J27" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K27" s="83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>53</v>
@@ -6795,22 +6795,22 @@
         <v>29</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="41"/>
       <c r="J28" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K28" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>53</v>
@@ -6822,22 +6822,22 @@
         <v>29</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="41"/>
       <c r="J29" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K29" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B30" s="72"/>
       <c r="C30" s="72"/>
@@ -6984,7 +6984,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -7037,7 +7037,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -7070,7 +7070,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -7097,7 +7097,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -7114,7 +7114,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -7170,7 +7170,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>21</v>
@@ -7182,22 +7182,22 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
       <c r="I13" s="41"/>
       <c r="J13" s="55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>21</v>
@@ -7212,18 +7212,18 @@
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="I14" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="J14" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="J14" s="55" t="s">
-        <v>387</v>
-      </c>
       <c r="K14" s="61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="165" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B15" s="41" t="s">
         <v>21</v>
@@ -7237,22 +7237,22 @@
       <c r="E15" s="51"/>
       <c r="F15" s="41"/>
       <c r="G15" s="56" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K15" s="76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="165" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>53</v>
@@ -7264,17 +7264,17 @@
         <v>29</v>
       </c>
       <c r="E16" s="107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K16" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -7408,7 +7408,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -7461,7 +7461,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -7521,7 +7521,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -7538,7 +7538,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -7592,7 +7592,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="65" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>21</v>
@@ -7607,10 +7607,10 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="54" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K13" s="175" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -7631,18 +7631,18 @@
       <c r="G14" s="26"/>
       <c r="H14" s="48"/>
       <c r="I14" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="137" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>21</v>
@@ -7655,20 +7655,20 @@
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="47"/>
       <c r="J15" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>21</v>
@@ -7680,22 +7680,22 @@
         <v>29</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K16" s="83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="63" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>53</v>
@@ -7707,22 +7707,22 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K17" s="83" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>21</v>
@@ -7734,22 +7734,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K18" s="83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B19" s="72"/>
       <c r="C19" s="72"/>
@@ -7764,7 +7764,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>21</v>
@@ -7779,15 +7779,15 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K20" s="86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>53</v>
@@ -7799,22 +7799,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K21" s="83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>53</v>
@@ -7826,22 +7826,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K22" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -7853,22 +7853,22 @@
         <v>29</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K23" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
@@ -8014,7 +8014,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -8067,7 +8067,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -8100,7 +8100,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -8127,7 +8127,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -8144,7 +8144,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="165" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -8214,22 +8214,22 @@
       <c r="E13" s="51"/>
       <c r="F13" s="41"/>
       <c r="G13" s="56" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="165" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>53</v>
@@ -8241,22 +8241,22 @@
         <v>29</v>
       </c>
       <c r="E14" s="107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
       <c r="J14" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K14" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>21</v>
@@ -8271,15 +8271,15 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K15" s="86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>53</v>
@@ -8291,22 +8291,22 @@
         <v>29</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K16" s="83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>53</v>
@@ -8318,22 +8318,22 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K17" s="74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -8345,22 +8345,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K18" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B19" s="72"/>
       <c r="C19" s="72"/>
@@ -8504,7 +8504,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -8557,7 +8557,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -8590,7 +8590,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -8617,7 +8617,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -8634,7 +8634,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -8688,7 +8688,7 @@
     </row>
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>21</v>
@@ -8707,15 +8707,15 @@
       <c r="H13" s="30"/>
       <c r="I13" s="164"/>
       <c r="J13" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" s="98" t="s">
         <v>301</v>
-      </c>
-      <c r="K13" s="98" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A14" s="33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>21</v>
@@ -8727,22 +8727,22 @@
         <v>43</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A15" s="33" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>51</v>
@@ -8754,19 +8754,19 @@
         <v>43</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I15" s="34"/>
       <c r="J15" s="34" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -8905,7 +8905,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -8958,7 +8958,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -8991,7 +8991,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -9018,7 +9018,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -9035,7 +9035,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="54" t="s">
         <v>21</v>
@@ -9104,10 +9104,10 @@
       <c r="H13" s="54"/>
       <c r="I13" s="54"/>
       <c r="J13" s="54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -9128,7 +9128,7 @@
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J14" s="24" t="s">
         <v>64</v>
@@ -9210,7 +9210,7 @@
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I17" s="24"/>
       <c r="J17" s="24" t="s">
@@ -9222,7 +9222,7 @@
     </row>
     <row r="18" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="84" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
@@ -9274,10 +9274,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="116" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="117" t="s">
         <v>130</v>
-      </c>
-      <c r="B1" s="117" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -9286,170 +9286,170 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="125" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="120" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="121"/>
       <c r="B4" s="122" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="123"/>
       <c r="B5" s="124" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="125" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="120" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="121"/>
       <c r="B7" s="122" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="123"/>
       <c r="B8" s="124" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="125" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="121"/>
       <c r="B10" s="122" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="123"/>
       <c r="B11" s="124" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="125" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>244</v>
-      </c>
-      <c r="B12" s="120" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="121"/>
       <c r="B13" s="122" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="123"/>
       <c r="B14" s="124" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="125" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="121"/>
       <c r="B16" s="122" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="123"/>
       <c r="B17" s="124" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="125" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B18" s="120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="121"/>
       <c r="B19" s="122" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="123"/>
       <c r="B20" s="124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="125" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B21" s="120" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="121"/>
       <c r="B22" s="122" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="123"/>
       <c r="B23" s="124" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="125" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B24" s="120" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="121"/>
       <c r="B25" s="122" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="123"/>
       <c r="B26" s="124" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="125" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B27" s="170" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -9480,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -9503,10 +9503,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="126" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -9517,18 +9517,18 @@
         <v>8</v>
       </c>
       <c r="G2" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H2" s="127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="126" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B3" s="105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7"/>
@@ -9539,18 +9539,18 @@
         <v>8</v>
       </c>
       <c r="G3" s="127" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="127" t="s">
         <v>94</v>
-      </c>
-      <c r="H3" s="127" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="126" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B4" s="105" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C4" s="130"/>
       <c r="D4" s="130"/>
@@ -9558,37 +9558,37 @@
         <v>7</v>
       </c>
       <c r="G4" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H4" s="127" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
       <c r="E5" s="129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G5" s="127" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H5" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="126" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="105" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="130"/>
       <c r="D6" s="130"/>
@@ -9596,18 +9596,18 @@
         <v>7</v>
       </c>
       <c r="G6" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H6" s="127" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="126" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C7" s="130"/>
       <c r="D7" s="130"/>
@@ -9615,18 +9615,18 @@
         <v>9</v>
       </c>
       <c r="G7" s="127" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="126" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="130"/>
       <c r="D8" s="130"/>
@@ -9634,18 +9634,18 @@
         <v>7</v>
       </c>
       <c r="G8" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H8" s="127" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="126" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="105" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C9" s="130"/>
       <c r="D9" s="130"/>
@@ -9653,18 +9653,18 @@
         <v>9</v>
       </c>
       <c r="G9" s="127" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H9" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="126" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B10" s="105" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C10" s="130"/>
       <c r="D10" s="130"/>
@@ -9672,18 +9672,18 @@
         <v>7</v>
       </c>
       <c r="G10" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="126" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B11" s="105" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C11" s="130"/>
       <c r="D11" s="130"/>
@@ -9691,18 +9691,18 @@
         <v>7</v>
       </c>
       <c r="G11" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H11" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="126" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B12" s="105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C12" s="130"/>
       <c r="D12" s="130"/>
@@ -9710,18 +9710,18 @@
         <v>7</v>
       </c>
       <c r="G12" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H12" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="126" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B13" s="105" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C13" s="130"/>
       <c r="D13" s="130"/>
@@ -9729,18 +9729,18 @@
         <v>9</v>
       </c>
       <c r="G13" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H13" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="126" t="s">
+        <v>392</v>
+      </c>
+      <c r="B14" s="105" t="s">
         <v>394</v>
-      </c>
-      <c r="B14" s="105" t="s">
-        <v>396</v>
       </c>
       <c r="C14" s="130"/>
       <c r="D14" s="130"/>
@@ -9748,18 +9748,18 @@
         <v>7</v>
       </c>
       <c r="G14" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H14" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="126" t="s">
+        <v>393</v>
+      </c>
+      <c r="B15" s="105" t="s">
         <v>395</v>
-      </c>
-      <c r="B15" s="105" t="s">
-        <v>397</v>
       </c>
       <c r="C15" s="130"/>
       <c r="D15" s="130"/>
@@ -9767,47 +9767,47 @@
         <v>9</v>
       </c>
       <c r="G15" s="127" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H15" s="127" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31.75" x14ac:dyDescent="0.45">
       <c r="A16" s="159" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B16" s="160" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C16" s="130"/>
       <c r="D16" s="130"/>
       <c r="E16" s="161" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F16" s="162"/>
       <c r="G16" s="163" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H16" s="163" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="131" t="s">
+        <v>292</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>303</v>
+      </c>
+      <c r="E17" s="129" t="s">
         <v>293</v>
       </c>
-      <c r="B17" s="105" t="s">
-        <v>304</v>
-      </c>
-      <c r="E17" s="129" t="s">
-        <v>294</v>
-      </c>
       <c r="G17" s="127" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H17" s="127" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -9852,44 +9852,44 @@
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="108" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="C2" s="109" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="D2" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="E2" s="110" t="s">
         <v>123</v>
-      </c>
-      <c r="E2" s="110" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="90.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" s="112" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" s="113" t="s">
         <v>57</v>
       </c>
       <c r="D3" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="114" t="s">
         <v>125</v>
-      </c>
-      <c r="E3" s="114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="111" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="133" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="113" t="s">
         <v>57</v>
@@ -9898,58 +9898,58 @@
         <v>57</v>
       </c>
       <c r="E4" s="114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="166" t="s">
+        <v>338</v>
+      </c>
+      <c r="B5" s="133" t="s">
         <v>339</v>
-      </c>
-      <c r="B5" s="133" t="s">
-        <v>340</v>
       </c>
       <c r="C5" s="113" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="114" t="s">
         <v>125</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="166" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6" s="133" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C6" s="113" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="114" t="s">
         <v>125</v>
-      </c>
-      <c r="E6" s="114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="26.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="166" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B7" s="133" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C7" s="113" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="114" t="s">
         <v>125</v>
-      </c>
-      <c r="E7" s="114" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -10069,7 +10069,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -10122,7 +10122,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -10182,7 +10182,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -10199,7 +10199,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10253,13 +10253,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
@@ -10268,10 +10268,10 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K13" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -10292,18 +10292,18 @@
       <c r="G14" s="26"/>
       <c r="H14" s="48"/>
       <c r="I14" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>21</v>
@@ -10317,47 +10317,47 @@
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="47"/>
       <c r="J15" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>86</v>
-      </c>
       <c r="E16" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K16" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>21</v>
@@ -10366,7 +10366,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -10374,15 +10374,15 @@
       <c r="H17" s="24"/>
       <c r="I17" s="41"/>
       <c r="J17" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="K17" s="83" t="s">
         <v>116</v>
-      </c>
-      <c r="K17" s="83" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>21</v>
@@ -10391,7 +10391,7 @@
         <v>22</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -10399,15 +10399,15 @@
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K18" s="83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="72"/>
       <c r="C19" s="72"/>
@@ -10422,7 +10422,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>21</v>
@@ -10437,51 +10437,51 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K20" s="86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>86</v>
-      </c>
       <c r="E21" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K21" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="41" t="s">
         <v>87</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>88</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
@@ -10489,15 +10489,15 @@
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K22" s="74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="71" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" s="72"/>
       <c r="C23" s="72"/>
@@ -10645,7 +10645,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -10698,7 +10698,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -10731,7 +10731,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -10758,7 +10758,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -10775,7 +10775,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10831,7 +10831,7 @@
     </row>
     <row r="13" spans="1:11" s="95" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="168" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>21</v>
@@ -10850,15 +10850,15 @@
       <c r="H13" s="30"/>
       <c r="I13" s="164"/>
       <c r="J13" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" s="169" t="s">
         <v>301</v>
-      </c>
-      <c r="K13" s="169" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B14" s="41" t="s">
         <v>21</v>
@@ -10872,22 +10872,22 @@
       <c r="E14" s="51"/>
       <c r="F14" s="41"/>
       <c r="G14" s="56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K14" s="76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="165" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>53</v>
@@ -10899,17 +10899,17 @@
         <v>29</v>
       </c>
       <c r="E15" s="107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K15" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -11044,7 +11044,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -11097,7 +11097,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -11157,7 +11157,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -11174,7 +11174,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -11228,13 +11228,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
@@ -11243,10 +11243,10 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K13" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -11265,22 +11265,22 @@
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="48"/>
       <c r="I14" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>21</v>
@@ -11294,20 +11294,20 @@
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="47"/>
       <c r="J15" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="71" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" s="72"/>
       <c r="C16" s="72"/>
@@ -11454,7 +11454,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -11507,7 +11507,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -11540,7 +11540,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -11567,7 +11567,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -11584,7 +11584,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -11640,13 +11640,13 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="143" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="144" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="144" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="143"/>
       <c r="E13" s="143"/>
@@ -11655,10 +11655,10 @@
       <c r="H13" s="143"/>
       <c r="I13" s="143"/>
       <c r="J13" s="54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K13" s="142" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -11677,22 +11677,22 @@
       <c r="E14" s="137"/>
       <c r="F14" s="137"/>
       <c r="G14" s="137" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="139"/>
       <c r="I14" s="140" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J14" s="137" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="141" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>21</v>
@@ -11706,20 +11706,20 @@
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H15" s="34"/>
       <c r="I15" s="47"/>
       <c r="J15" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K15" s="83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="145" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>21</v>
@@ -11728,7 +11728,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -11736,15 +11736,15 @@
       <c r="H16" s="29"/>
       <c r="I16" s="146"/>
       <c r="J16" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="K16" s="147" t="s">
         <v>145</v>
-      </c>
-      <c r="K16" s="147" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B17" s="144" t="s">
         <v>21</v>
@@ -11759,15 +11759,15 @@
       <c r="H17" s="143"/>
       <c r="I17" s="143"/>
       <c r="J17" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="K17" s="142" t="s">
         <v>148</v>
-      </c>
-      <c r="K17" s="142" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>21</v>
@@ -11779,22 +11779,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="K18" s="61" t="s">
         <v>155</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="148" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>51</v>
@@ -11806,24 +11806,24 @@
         <v>29</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I19" s="41"/>
       <c r="J19" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19" s="61" t="s">
         <v>159</v>
-      </c>
-      <c r="K19" s="61" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="148" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>53</v>
@@ -11835,22 +11835,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="I20" s="41"/>
       <c r="J20" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K20" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="148" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>53</v>
@@ -11862,22 +11862,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K21" s="61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="148" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>53</v>
@@ -11889,22 +11889,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K22" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A23" s="148" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>53</v>
@@ -11916,22 +11916,22 @@
         <v>29</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="I23" s="41"/>
       <c r="J23" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K23" s="61" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A24" s="148" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>53</v>
@@ -11943,22 +11943,22 @@
         <v>29</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="41"/>
       <c r="J24" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K24" s="61" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
@@ -11973,7 +11973,7 @@
     </row>
     <row r="26" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="71" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B26" s="72"/>
       <c r="C26" s="72"/>
@@ -12121,7 +12121,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -12174,7 +12174,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -12207,7 +12207,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12234,7 +12234,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12251,7 +12251,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -12307,7 +12307,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="171" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B13" s="136" t="s">
         <v>21</v>
@@ -12323,18 +12323,18 @@
       <c r="G13" s="137"/>
       <c r="H13" s="139"/>
       <c r="I13" s="140" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J13" s="137" t="s">
+        <v>192</v>
+      </c>
+      <c r="K13" s="141" t="s">
         <v>193</v>
-      </c>
-      <c r="K13" s="141" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="172" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>53</v>
@@ -12346,22 +12346,22 @@
         <v>29</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="47"/>
       <c r="J14" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="K14" s="83" t="s">
         <v>196</v>
-      </c>
-      <c r="K14" s="83" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="143" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B15" s="144" t="s">
         <v>21</v>
@@ -12376,7 +12376,7 @@
       <c r="H15" s="143"/>
       <c r="I15" s="143"/>
       <c r="J15" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K15" s="142" t="s">
         <v>2</v>
@@ -12384,7 +12384,7 @@
     </row>
     <row r="16" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="148" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>21</v>
@@ -12396,22 +12396,22 @@
         <v>29</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="41"/>
       <c r="J16" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K16" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="148" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>51</v>
@@ -12423,24 +12423,24 @@
         <v>29</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K17" s="61" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>53</v>
@@ -12452,22 +12452,22 @@
         <v>29</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="I18" s="41"/>
       <c r="J18" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="K18" s="61" t="s">
         <v>165</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="148" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>53</v>
@@ -12479,22 +12479,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="I19" s="41"/>
       <c r="J19" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K19" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>53</v>
@@ -12506,22 +12506,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="I20" s="41"/>
       <c r="J20" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K20" s="61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>53</v>
@@ -12533,22 +12533,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="41"/>
       <c r="J21" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>53</v>
@@ -12560,22 +12560,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="I22" s="41"/>
       <c r="J22" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K22" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="17" customFormat="1" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B23" s="72"/>
       <c r="C23" s="72"/>
@@ -12722,7 +12722,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -12775,7 +12775,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>59</v>
@@ -12808,7 +12808,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12835,7 +12835,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
@@ -12852,7 +12852,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -12908,7 +12908,7 @@
     </row>
     <row r="13" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="165" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>21</v>
@@ -12917,7 +12917,7 @@
         <v>22</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="41"/>
@@ -12925,15 +12925,15 @@
       <c r="H13" s="41"/>
       <c r="I13" s="41"/>
       <c r="J13" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" s="76" t="s">
         <v>208</v>
-      </c>
-      <c r="K13" s="76" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="165" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>51</v>
@@ -12942,20 +12942,20 @@
         <v>22</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="51"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K14" s="77" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -13089,7 +13089,7 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="I4" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>27</v>
@@ -13142,7 +13142,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="97" t="s">
         <v>59</v>
@@ -13202,7 +13202,7 @@
         <v>41</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
@@ -13219,7 +13219,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -13273,7 +13273,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="173" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B13" s="40" t="s">
         <v>21</v>
@@ -13289,18 +13289,18 @@
       <c r="G13" s="26"/>
       <c r="H13" s="48"/>
       <c r="I13" s="49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>54</v>
       </c>
       <c r="K13" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="172" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>21</v>
@@ -13314,26 +13314,26 @@
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" s="34"/>
       <c r="I14" s="47"/>
       <c r="J14" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K14" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="173" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>53</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>26</v>
@@ -13343,24 +13343,24 @@
       <c r="G15" s="26"/>
       <c r="H15" s="48"/>
       <c r="I15" s="49" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J15" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="K15" s="70" t="s">
         <v>238</v>
-      </c>
-      <c r="K15" s="70" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="172" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="41" t="s">
         <v>26</v>
@@ -13369,16 +13369,16 @@
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
       <c r="H16" s="34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J16" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="K16" s="83" t="s">
         <v>240</v>
-      </c>
-      <c r="K16" s="83" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="13.3" thickBot="1" x14ac:dyDescent="0.45">
@@ -13412,12 +13412,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D83CB400C3424C4590915CF6C5E758B7" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7cb2b26aaf8d99e710797990a2b1c47">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3b615667-b975-40b1-ae5a-ef4d6726c426" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d61f9b077eef3841a59297a4bf8056c9" ns2:_="">
     <xsd:import namespace="3b615667-b975-40b1-ae5a-ef4d6726c426"/>
@@ -13555,6 +13549,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65E5A92E-C191-4A71-B1E7-50CA46998E16}">
   <ds:schemaRefs>
@@ -13564,15 +13564,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1B6951-90F6-4939-9AC0-9F1A59AE0CAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01814C20-87D5-416B-8528-D2BB09E83DFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13588,4 +13579,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1B6951-90F6-4939-9AC0-9F1A59AE0CAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>